--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. SINIF 2 SAAT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Açıklamalar ve Onay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'11. SINIF 2 SAAT'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Açıklamalar ve Onay'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -1671,668 +1673,795 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
     </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+  </sheetData>
+  <mergeCells count="67">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="E9:E11"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LGNL-CYP-CP-004 · okulapp.org&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.3" customWidth="1" min="1" max="1"/>
+    <col width="9.01" customWidth="1" min="2" max="2"/>
+    <col width="4.77" customWidth="1" min="3" max="3"/>
+    <col width="10.6" customWidth="1" min="4" max="4"/>
+    <col width="13.78" customWidth="1" min="5" max="5"/>
+    <col width="29.68" customWidth="1" min="6" max="6"/>
+    <col width="50.88" customWidth="1" min="7" max="7"/>
+    <col width="13.25" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>[OKUL ADI]</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 2026-2027 EĞİTİM ÖĞRETİM YILI 11. SINIF SEÇMELİ COĞRAFYA DERSİ (HAFTADA 2 SAAT) YILLIK PLANI — AÇIKLAMALAR VE ONAY</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ÖĞRENME KANITLARI (ÖLÇME VE DEĞERLENDİRME) — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
-      <c r="H50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="45.4" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="45.4" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1-3. haftalar</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktısı; açık uçlu sorular, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden bir belgesel, kitap veya bilimsel çalışmalardan (makale, bildiri, proje vb.) yola çıkarak mekânsal sorunların çözümünde coğrafyanın katkılarını içeren bir rapor hazırlamaları istenebilir. Performans görevi; bilgi toplama, bilgileri düzenlenme ve rapor hazırlama ölçütlerine göre değerlendirilebilir</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="45.4" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="45.4" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>4-6. haftalar, 7-9. haftalar</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktısı; kontrol listesi, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu, grup değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden çeşitli mekânsal verileri kullanarak web tabanlı CBS üzerinden basit bir harita oluşturmaları istenebilir. Performans görevi; harita okuma, haritayı çözümleme, haritadan çıkarım yapma ve harita oluşturma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="56" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>10-13. haftalar, 14-17. haftalar</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; kavram haritası, çalışma yaprağı, açık uçlu sorular, grup değerlendirme formu, açık uçlu sorular, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden Türkiye’de yer alan su kaynaklarından (deniz, göl, akarsu vb.) birini seçmeleri, seçtikleri su kaynağının kullanımı, yönetimi ve bu su kaynağında kullanıma bağlı olarak meydana gelen değişimleri araştırmaları istenebilir. Performans ürünü; rapor, broşür, sunum vb. şekilde hazırlanabilir. Performans görevi; bilgi toplama, bilgileri düzenlenme, rapor hazırlama ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="45.4" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="45.4" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>19-21. haftalar</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; çalışma yaprağı, açık uçlu sorular, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden yaşadıkları çevrede bulunan yerleşmelerin mekânsal organizasyonunu çözümlemeleri ve bu organizasyona ilişkin öngörülerini sunmaları istenebilir. Performans görevi; bilgi toplama, bilgileri düzenleme, ilişki kurma, sonuç çıkarma ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="45.4" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="45.4" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>22. hafta, 23-24. haftalar, 25-26. haftalar, 27-28. haftalar</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; öz değerlendirme formu, açık uçlu sorular, çalışma yaprağı, akran değerlendirme formu, bütüncül dereceli puanlama anahtarı, performans görevi, analitik dereceli puanlama anahtarı kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden gıda güvencesinin küresel iklim değişikliği ve nüfus artışına bağlı olarak gelecekteki durumuna yönelik bilgi görseli hazırlamaları istenebilir. Performans görevi; hazırlık yapma, bilgi toplama, bilgileri çözümleme, bilgi görseli oluşturma ve sunma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="56" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>29-31. haftalar</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; yapılandırılmış grid, bütünsel dereceli puanlama anahtarı, öz değerlendirme formu, açık uçlu sorular, performans görevi, analitik dereceli puanlama anahtarı, grup değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden küresel iklim değişikliğinin etkilerini azaltma ve iklim değişikliğine uyum sağlamaya yönelik stratejiler hakkında grup hâlinde görüş geliştirmeleri ve su kaynaklarının etkilerine yönelik ortak bir rapor hazırlamaları istenebilir. Performans görevi; bilgi toplama, bilgileri düzenleme, çıkarım yapma ve rapor hazırlama ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="56" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>32-33. haftalar, 34-35. haftalar</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; çalışma yaprağı, açık uçlu sorular, kontrol listesi, akran değerlendirme formu, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden Türk İşbirliği ve Koordinasyon Ajansı Başkanlığı’nın (TİKA) Türkiye’nin kültürel hinterlandındaki faaliyet ve etkilerinin değerlendirilmesine yönelik hazırlayacakları haberi sunmaları istenebilir. Performans görevi; bilgi toplama, bilgileri düzenlenme ve görselleştirme, ilişki kurma, sonuç çıkarma ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>SOSYAL - DUYGUSAL ÖĞRENME BECERİLERİ — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-    </row>
-    <row r="60" ht="24.2" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="24.2" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>1-3. haftalar</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.3. Sosyal Farkındalık, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="34.8" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="34.8" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>4-6. haftalar, 7-9. haftalar, 19-21. haftalar</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.2. İş Birliği</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="24.2" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="24.2" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10-13. haftalar, 14-17. haftalar</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB2.1. İletişim, SDB2.2. İş Birliği, SDB2.3. Sosyal Farkındalık, SDB3.1. Uyum, SDB3.2. Esneklik, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="45.4" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="45.4" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>22. hafta, 23-24. haftalar, 25-26. haftalar, 27-28. haftalar</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.2. İş Birliği, SDB2.3. Sosyal Farkındalık, SDB3.3 Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="24.2" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="24.2" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>29-31. haftalar</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Öz Yansıtma, SDB2.1. İletişim, SDB2.2. İş Birliği, SDB2.3. Sosyal Farkındalık, SDB3.1. Uyum, SDB3.2. Esneklik, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="24.2" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="24.2" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>32-33. haftalar, 34-35. haftalar</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.2. İş Birliği, SDB2.3. Sosyal Farkındalık</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>DEĞERLER — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
-      <c r="H67" s="12" t="n"/>
-    </row>
-    <row r="68" ht="13.6" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="13.6" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>1-3. haftalar</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-    </row>
-    <row r="69" ht="24.2" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="24.2" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>4-6. haftalar, 7-9. haftalar</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D7. Estetik, D8. Mahremiyet</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="24.2" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="24.2" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>10-13. haftalar, 14-17. haftalar</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>D17. Tasarruf, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="13.6" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="13.6" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>19-21. haftalar</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D5. Duyarlılık</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-    </row>
-    <row r="72" ht="45.4" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="45.4" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>22. hafta, 23-24. haftalar, 25-26. haftalar, 27-28. haftalar</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>D5. Duyarlılık, D13. Sağlıklı Yaşam, D17. Tasarruf, D18. Temizlik, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-    </row>
-    <row r="73" ht="13.6" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="13.6" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>29-31. haftalar</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>D5. Duyarlılık, D14. Saygı, D17. Tasarruf, D18. Temizlik, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
-    </row>
-    <row r="74" ht="24.2" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="24.2" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>32-33. haftalar, 34-35. haftalar</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D14. Saygı, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>OKURYAZARLIK BECERİLERİ — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
-      <c r="H76" s="12" t="n"/>
-    </row>
-    <row r="77" ht="24.2" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="24.2" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>1-3. haftalar, 19-21. haftalar</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n"/>
-      <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="24.2" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="24.2" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>4-6. haftalar, 7-9. haftalar</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n"/>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>OB2. Dijital Okuryazarlık, OB4. Görsel Okuryazarlık, OB7. Veri Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-    </row>
-    <row r="79" ht="45.4" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="45.4" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>10-13. haftalar, 14-17. haftalar, 29-31. haftalar</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı, OB8. Sürdürülebilirlik Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="45.4" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="45.4" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>22. hafta, 23-24. haftalar, 25-26. haftalar, 27-28. haftalar</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n"/>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı, OB2. Dijital Okuryazarlık, OB7. Veri Okuryazarlığı, OB8. Sürdürülebilirlik Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="24.2" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="24.2" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>32-33. haftalar, 34-35. haftalar</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n"/>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı, OB4. Görsel Okuryazarlık, OB5. Kültür Okuryazarlığı, OB7. Veri Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="n"/>
-      <c r="G81" s="2" t="n"/>
-      <c r="H81" s="2" t="n"/>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>FARKLILAŞTIRMA</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
-      <c r="H83" s="12" t="n"/>
-    </row>
-    <row r="84" ht="45.4" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="45.4" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Türkiye Yüzyılı Maarif Modeli Ortak Metni'nde “Farklılaştırılmış öğrenme yaşantılarında öğrencilerin ilgi alanları ile öğrenme profilleri önemlidir ve öğrencilere çeşitli öğrenme yaşantıları sunulur. Farklılaştırma kapsamında yapılacak zenginleştirme ve destekleme uygulamalarında öğrencilerin bireysel farklılıkları (öğrenme hızları, öğrenme stilleri, yetenekleri vb.), ilgi ve ihtiyaçları dikkate alınarak gereken planlamalar yapılır.” ifadesi yer almaktadır. Öğretmenler sınıftaki öğrencilerini gözlemleyerek gerek gördükleri konularda farklılaştırma uygulamalarını ders sürecine dâhil etmelidirler.</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n"/>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>OKUL TEMELLİ PLANLAMA — ÇERÇEVE PLAN AÇIKLAMASI</t>
         </is>
       </c>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="12" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="12" t="n"/>
-      <c r="H86" s="12" t="n"/>
-    </row>
-    <row r="87" ht="66.59999999999999" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="66.59999999999999" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Okul temelli planlama; zümre öğretmenler kurulu tarafından ders kapsamında gerçekleştirilmesi kararlaştırılan araştırma ve gözlem, sosyal etkinlikler, proje çalışmaları, yerel çalışmalar, okuma çalışmaları vb. çalışmaları kapsamaktadır. Çalışmalar için ayrılan süre eğitim-öğretim yılı içinde planlanır ve yıllık planlarda ifade edilir. Bu planlamalar kapsamında yürütülecek öğretim faaliyetleri; öğrenci katılımını desteklemeli, yaparak ve yaşayarak öğrenmeye olanak tanımalı, öğrencinin bütüncül gelişime hizmet etmelidir. *Bu çerçeve planda belirtilen okul temelli planlama haftaları örnek olarak sunulmuştur. Zümre öğretmenler kurulunda aldığınız karara göre okul ve ders koşullarınıza uygun (öğretim programında belirtilen okul temelli planlama ders saati 2 haftadan fazla sürebilir) düzenleyebilirsiniz.</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>OKUL UYARLAMA NOTLARI</t>
         </is>
       </c>
-      <c r="B89" s="12" t="n"/>
-      <c r="C89" s="12" t="n"/>
-      <c r="D89" s="12" t="n"/>
-      <c r="E89" s="12" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="12" t="n"/>
-      <c r="H89" s="12" t="n"/>
-    </row>
-    <row r="90" ht="24.2" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="24.2" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>GENEL ŞABLON: Bu plan, okulapp.org belge arşivinde yayımlanan genel sürümdür (CC BY 4.0). Köşeli parantezli KIRMIZI alanlar (okul adı, ad-soyad, tarih) okulun bilgileriyle doldurulur; doldurduktan sonra parantez kaldırılır ve yazı rengi siyaha çevrilir.</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-    </row>
-    <row r="91" ht="34.8" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="34.8" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "11. SINIF 2 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
-      <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2" t="n"/>
-    </row>
-    <row r="92" ht="45.4" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="45.4" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="34.8" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="34.8" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n"/>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
-      <c r="F93" s="2" t="n"/>
-      <c r="G93" s="2" t="n"/>
-      <c r="H93" s="2" t="n"/>
-    </row>
-    <row r="94" ht="13.6" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="13.6" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n"/>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
-    </row>
-    <row r="95" ht="13.6" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="13.6" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2" t="n"/>
-    </row>
-    <row r="97" ht="24.2" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+    </row>
+    <row r="50" ht="24.2" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2347,311 +2476,245 @@
           </r>
         </is>
       </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-    </row>
-    <row r="99" ht="13" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H99" s="12" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="H52" s="12" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="2" t="n"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="13" t="inlineStr">
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="2" t="n"/>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="13" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="2" t="n"/>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="13" t="inlineStr">
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="2" t="n"/>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="13" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="2" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="14" t="inlineStr">
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="16" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="155">
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C72:H72"/>
+  <mergeCells count="89">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="C78:H78"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A106:H106"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="C79:H79"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="C73:H73"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C69:H69"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="C56:H56"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="C53:H53"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C68:H68"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C80:H80"/>
-    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C51:H51"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="C70:H70"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="C7:H7"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -1612,66 +1612,6 @@
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="67">

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-004_Cografya_11_Sinif_Secmeli_2_Saat_Yillik_Plani_v1.0.xlsx
@@ -1702,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -2333,7 +2333,7 @@
     <row r="44" ht="34.8" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "11. SINIF 2 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
+          <t>ÖĞRETİM PROGRAMI: Bu plan, Coğrafya Dersi Öğretim Programına (Türkiye Yüzyılı Maarif Modeli) göre hazırlanmıştır. Program, Talim ve Terbiye Kurulunun 23.05.2024 tarihli ve 20 sayılı kararıyla kabul edilmiş; Kurulun 13.05.2026 tarihli ve 53 sayılı kararıyla değişiklik yapılarak 2026-2027 eğitim ve öğretim yılında 9, 10 ve 11. sınıf seviyelerinde uygulanmak üzere yürürlüğe konulmuştur. Esas alınacak metin programın 2026 nüshasıdır (mufredat.meb.gov.tr).</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -2344,10 +2344,10 @@
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
     </row>
-    <row r="45" ht="45.4" customHeight="1">
+    <row r="45" ht="24.2" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
+          <t>İKİ DERS SAATİ UYGULAMASI: Programın 1.4 numaralı bölümü uyarınca iki ders saatlik uygulamada ünite yapısı korunur, orada belirtilen öğrenme çıktıları işlenir; bu plan çerçeve planın iki saatlik sayfasından türetildiği için o listeyi yansıtır.</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -2361,7 +2361,7 @@
     <row r="46" ht="34.8" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
+          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "11. SINIF 2 SAAT" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -2372,10 +2372,10 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
-    <row r="47" ht="13.6" customHeight="1">
+    <row r="47" ht="45.4" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
+          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -2386,10 +2386,10 @@
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
     </row>
-    <row r="48" ht="13.6" customHeight="1">
+    <row r="48" ht="34.8" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+          <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -2400,8 +2400,36 @@
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
     </row>
-    <row r="50" ht="24.2" customHeight="1">
+    <row r="49" ht="13.6" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="13.6" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24.2" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2416,71 +2444,35 @@
           </r>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>[Adı SOYADI]</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>[Adı SOYADI]</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Coğrafya Öğretmeni</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="2" t="n"/>
+      <c r="H54" s="12" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="13" t="inlineStr">
@@ -2493,7 +2485,7 @@
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Coğrafya Öğretmeni</t>
+          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -2536,40 +2528,78 @@
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="2" t="n"/>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>[Adı SOYADI]</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Coğrafya Öğretmeni</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>[Adı SOYADI]</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Coğrafya Öğretmeni</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="89">
+  <mergeCells count="91">
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="G57:H57"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A50:H50"/>
@@ -2578,23 +2608,23 @@
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A54:D54"/>
+    <mergeCell ref="G58:H58"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="E53:F53"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G59:H59"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A47:H47"/>
@@ -2606,15 +2636,15 @@
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C4:H4"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C17:H17"/>
+    <mergeCell ref="E59:F59"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A32:B32"/>
@@ -2626,12 +2656,12 @@
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="E56:F56"/>
     <mergeCell ref="G56:H56"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A39:H39"/>
-    <mergeCell ref="G52:H52"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="A36:H36"/>
@@ -2642,7 +2672,6 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C23:H23"/>
-    <mergeCell ref="G53:H53"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A46:H46"/>
@@ -2652,6 +2681,7 @@
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A31:B31"/>
